--- a/data/reports/2024-03-25/2024-03-25_duplicates.xlsx
+++ b/data/reports/2024-03-25/2024-03-25_duplicates.xlsx
@@ -140,7 +140,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ff8966501bb7f810027562cae54bcb7f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004801</t>
+    <t>RMD0004807</t>
   </si>
   <si>
     <t>E-Vergent.Com LLC</t>
@@ -153,12 +153,6 @@
     <t>none</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004807</t>
-  </si>
-  <si>
     <t>Shawn Tarlo</t>
   </si>
   <si>
@@ -184,7 +178,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005143</t>
+    <t>RMD0004801</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004495</t>
   </si>
   <si>
     <t>Ooma, Inc.</t>
@@ -195,6 +195,30 @@
 SUNNYVALE CA 94085</t>
   </si>
   <si>
+    <t>0023473408; 0025715012; 0028440600; 0021330824; 0022722623</t>
+  </si>
+  <si>
+    <t>Tobin Farrand</t>
+  </si>
+  <si>
+    <t>Vice President, Engineering &amp; Operations</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Operations</t>
+  </si>
+  <si>
+    <t>6505666600</t>
+  </si>
+  <si>
+    <t>2024-02-26</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cff38bf91b05f4109294113d9c4bcb69&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005143</t>
+  </si>
+  <si>
     <t>0023473408
 0025715012
 0028440600</t>
@@ -213,31 +237,7 @@
 SUNNYVALE CA 94085</t>
   </si>
   <si>
-    <t>6505666600</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b165a0c21b0e3410503110ad9c4bcbce&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004495</t>
-  </si>
-  <si>
-    <t>0023473408; 0025715012; 0028440600; 0021330824; 0022722623</t>
-  </si>
-  <si>
-    <t>Tobin Farrand</t>
-  </si>
-  <si>
-    <t>Vice President, Engineering &amp; Operations</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Operations</t>
-  </si>
-  <si>
-    <t>2024-02-26</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cff38bf91b05f4109294113d9c4bcb69&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005813</t>
@@ -280,7 +280,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009352</t>
+    <t>RMD0004139</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -296,6 +296,21 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>800-709-6314</t>
+  </si>
+  <si>
+    <t>2022-09-15</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009352</t>
+  </si>
+  <si>
     <t>Financial</t>
   </si>
   <si>
@@ -306,21 +321,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004139</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>800-709-6314</t>
-  </si>
-  <si>
-    <t>2022-09-15</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -430,7 +430,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0006774</t>
+    <t>RMD0008869</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -440,40 +440,40 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>Sage Network &amp; Communications</t>
+  </si>
+  <si>
+    <t>Rick Minyard</t>
+  </si>
+  <si>
+    <t>Officer</t>
+  </si>
+  <si>
+    <t>Exec</t>
+  </si>
+  <si>
+    <t>8059141801</t>
+  </si>
+  <si>
+    <t>1855</t>
+  </si>
+  <si>
+    <t>2024-02-02</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
+  </si>
+  <si>
     <t>NONE</t>
   </si>
   <si>
-    <t>Sage Network &amp; Communications</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
-  </si>
-  <si>
-    <t>Rick Minyard</t>
-  </si>
-  <si>
-    <t>Officer</t>
-  </si>
-  <si>
-    <t>Exec</t>
-  </si>
-  <si>
-    <t>8059141801</t>
-  </si>
-  <si>
-    <t>1855</t>
-  </si>
-  <si>
-    <t>2024-02-02</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003929</t>
+    <t>RMD0004389</t>
   </si>
   <si>
     <t>Idealtel Dominicana USA, Inc. dba myidealtel.com</t>
@@ -484,16 +484,16 @@
 Cooper City FL 33328</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003929</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004389</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
+    <t>RMD0004724</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -503,16 +503,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005819</t>
+  </si>
+  <si>
     <t>4109121000</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004724</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004806</t>
@@ -553,10 +553,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=beda02fb1bc5f05064c4426de54bcb94&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -567,20 +577,33 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -614,33 +637,30 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+    <t>RMD0008297</t>
+  </si>
+  <si>
+    <t>GloTell US Corp.</t>
+  </si>
+  <si>
+    <t>1830 S Ocean Drive
+Suite 902
+Halladale Beach FL 33009</t>
+  </si>
+  <si>
+    <t>Alina Karpova</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>9548354110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0002900</t>
-  </si>
-  <si>
-    <t>GloTell US Corp.</t>
   </si>
   <si>
     <t>1001 North Federal Hwy
@@ -667,26 +687,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0a82aeaf1b7430507ccf20ecac4bcb54&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008297</t>
-  </si>
-  <si>
-    <t>1830 S Ocean Drive
-Suite 902
-Halladale Beach FL 33009</t>
-  </si>
-  <si>
-    <t>Alina Karpova</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>9548354110</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0009294</t>
   </si>
   <si>
@@ -763,7 +763,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005124</t>
+    <t>RMD0005139</t>
   </si>
   <si>
     <t>Opentact Inc</t>
@@ -774,12 +774,6 @@
 Cheyenne WY 82009</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005139</t>
-  </si>
-  <si>
     <t>Anne Kwong</t>
   </si>
   <si>
@@ -802,6 +796,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005124</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0004701</t>
   </si>
   <si>
@@ -848,7 +848,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003053</t>
+    <t>RMD0009640</t>
   </si>
   <si>
     <t>The Kalson Inc Limited</t>
@@ -858,22 +858,22 @@
  UB10 0AD UXBRIDGE, United Kingdom</t>
   </si>
   <si>
+    <t>Anum Rasheed Kalson</t>
+  </si>
+  <si>
+    <t>'+92-3222100249</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003053</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=73375fbb1b30b0507ccf20ecac4bcb1c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009640</t>
-  </si>
-  <si>
-    <t>Anum Rasheed Kalson</t>
-  </si>
-  <si>
-    <t>'+92-3222100249</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
+    <t>RMD0003444</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -884,6 +884,32 @@
   </si>
   <si>
     <t>Canada</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -903,33 +929,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007384</t>
+    <t>RMD0003705</t>
   </si>
   <si>
     <t>Axkan Consultores S. de R.L. de C.V.</t>
@@ -942,6 +942,12 @@
     <t>Mexico</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007384</t>
+  </si>
+  <si>
     <t>Juan Carlos Bravo Abarca</t>
   </si>
   <si>
@@ -949,12 +955,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=47035e5e1b7eb4109ac2ea04bc4bcbb1&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003705</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009817</t>
@@ -1064,7 +1064,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -1077,22 +1077,22 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -1106,6 +1106,18 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -1119,19 +1131,29 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+    <t>RMD0007962</t>
+  </si>
+  <si>
+    <t>office no 17 3rd floor anique arcade pla
+federal 46000 Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Umair Hassan</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>'+92-333-6778-636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0006284</t>
@@ -1141,29 +1163,7 @@
   Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007962</t>
-  </si>
-  <si>
-    <t>office no 17 3rd floor anique arcade pla
-federal 46000 Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>Umair Hassan</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>'+92-333-6778-636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -1195,7 +1195,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
+    <t>RMD0007626</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1208,16 +1208,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007575</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1227,16 +1227,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1246,6 +1246,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1258,13 +1264,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008097</t>
+    <t>RMD0008064</t>
   </si>
   <si>
     <t>Sam Asher Computing Services, Inc.</t>
@@ -1279,6 +1279,12 @@
 Hyper-Reach</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008097</t>
+  </si>
+  <si>
     <t>Caitlin Olfano</t>
   </si>
   <si>
@@ -1291,13 +1297,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4172e7f21b7a3810dcd1ed3be54bcbb5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008064</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008393</t>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1305,12 +1305,6 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1328,6 +1322,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008393</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008451</t>
   </si>
   <si>
@@ -1347,7 +1347,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008611</t>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1357,6 +1357,21 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
@@ -1372,44 +1387,29 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008756</t>
+    <t>RMD0008759</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>Jeffrey D Houston</t>
+  </si>
+  <si>
+    <t>6039294272</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008756</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
-  </si>
-  <si>
-    <t>Jeffrey D Houston</t>
-  </si>
-  <si>
-    <t>6039294272</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008755</t>
@@ -1476,7 +1476,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009160</t>
+    <t>RMD0009161</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1486,16 +1486,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>9497014500</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009160</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009161</t>
-  </si>
-  <si>
-    <t>9497014500</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -1530,7 +1530,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=af63c18f1b3bb010c8e0ed3ce54bcb41&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009728</t>
+    <t>RMD0009729</t>
   </si>
   <si>
     <t>Huffman Telcom Corp</t>
@@ -1540,22 +1540,22 @@
 Fort Collins CO 80524</t>
   </si>
   <si>
+    <t>Charlie Huffman</t>
+  </si>
+  <si>
+    <t>Customer Services</t>
+  </si>
+  <si>
+    <t>'+13033140978</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009728</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=a48d8f371bac051085edebdbac4bcbba&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009729</t>
-  </si>
-  <si>
-    <t>Charlie Huffman</t>
-  </si>
-  <si>
-    <t>Customer Services</t>
-  </si>
-  <si>
-    <t>'+13033140978</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0013578</t>
@@ -5907,31 +5907,47 @@
       <c r="I5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U5" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="V5" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1">
         <v>16082927</v>
@@ -5957,40 +5973,24 @@
       <c r="I6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
         <v>53</v>
       </c>
@@ -6028,29 +6028,29 @@
       <c r="L7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U7" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V7" s="1" t="s">
         <v>63</v>
       </c>
@@ -6088,29 +6088,29 @@
       <c r="L8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="N8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="U8" s="1"/>
       <c r="V8" s="1" t="s">
         <v>70</v>
       </c>
@@ -6244,15 +6244,9 @@
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
         <v>87</v>
       </c>
@@ -6273,13 +6267,13 @@
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T11" s="1" t="s">
         <v>29</v>
@@ -6310,9 +6304,15 @@
       <c r="F12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J12" s="1" t="s">
         <v>87</v>
       </c>
@@ -6333,13 +6333,13 @@
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T12" s="1" t="s">
         <v>29</v>
@@ -6686,38 +6686,54 @@
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R19" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U19" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>140</v>
+      </c>
       <c r="V19" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B20" s="1">
         <v>23250467</v>
@@ -6734,47 +6750,31 @@
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>143</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
         <v>144</v>
       </c>
@@ -6889,28 +6889,14 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>154</v>
-      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q23" s="1"/>
       <c r="R23" s="1" t="s">
         <v>29</v>
       </c>
@@ -6918,16 +6904,16 @@
         <v>29</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B24" s="1">
         <v>25462672</v>
@@ -6947,14 +6933,28 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>156</v>
+      </c>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R24" s="1" t="s">
         <v>29</v>
       </c>
@@ -6962,7 +6962,7 @@
         <v>29</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1" t="s">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>29</v>
@@ -7194,40 +7194,34 @@
       <c r="L29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B30" s="1">
         <v>27710730</v>
@@ -7236,7 +7230,7 @@
         <v>178</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>29</v>
@@ -7248,35 +7242,41 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="N30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1"/>
       <c r="V30" s="1" t="s">
         <v>194</v>
       </c>
@@ -7301,47 +7301,47 @@
         <v>33</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>198</v>
-      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="M31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R31" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B32" s="1">
         <v>27967686</v>
@@ -7350,7 +7350,7 @@
         <v>196</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>29</v>
@@ -7359,19 +7359,21 @@
         <v>33</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>204</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>205</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>33</v>
@@ -7380,17 +7382,15 @@
         <v>208</v>
       </c>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U32" s="1"/>
       <c r="V32" s="1" t="s">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>26</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>26</v>
@@ -7643,31 +7643,47 @@
       <c r="I37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R37" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U37" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>241</v>
+      </c>
       <c r="V37" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B38" s="1">
         <v>30149645</v>
@@ -7693,40 +7709,24 @@
       <c r="I38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>242</v>
-      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>243</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
         <v>244</v>
       </c>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -7811,13 +7811,13 @@
         <v>256</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>248</v>
@@ -7875,31 +7875,45 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>264</v>
+      </c>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="Q41" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R41" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B42" s="1">
         <v>31063506</v>
@@ -7919,36 +7933,22 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>266</v>
-      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -7981,31 +7981,45 @@
       <c r="I43" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>277</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R43" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B44" s="1">
         <v>31064850</v>
@@ -8023,42 +8037,28 @@
         <v>271</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="O44" s="1" t="s">
         <v>281</v>
       </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8087,45 +8087,31 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>288</v>
-      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B46" s="1">
         <v>31092349</v>
@@ -8145,22 +8131,36 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>290</v>
+      </c>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
+      <c r="Q46" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R46" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="P51" s="1"/>
       <c r="Q51" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>26</v>
@@ -8515,31 +8515,45 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>331</v>
+      </c>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
+      <c r="Q53" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R53" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B54" s="1">
         <v>31294614</v>
@@ -8559,36 +8573,22 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>333</v>
-      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q54" s="1"/>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8620,46 +8620,40 @@
       <c r="H55" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
+      <c r="I55" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>343</v>
       </c>
       <c r="P55" s="1"/>
       <c r="Q55" s="1" t="s">
         <v>38</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B56" s="1">
         <v>31356652</v>
@@ -8680,33 +8674,39 @@
         <v>338</v>
       </c>
       <c r="H56" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="M56" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1" t="s">
         <v>38</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1" t="s">
@@ -8730,47 +8730,55 @@
       <c r="F57" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>353</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B58" s="1">
         <v>31392434</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>26</v>
@@ -8778,39 +8786,31 @@
       <c r="F58" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>356</v>
-      </c>
+      <c r="G58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
@@ -8846,7 +8846,7 @@
         <v>362</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>360</v>
@@ -8858,10 +8858,10 @@
         <v>363</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>26</v>
@@ -9028,9 +9028,15 @@
       <c r="F63" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -9072,15 +9078,9 @@
       <c r="F64" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -9117,55 +9117,39 @@
         <v>382</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-      <c r="J65" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="66" spans="1:22">
       <c r="A66" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B66" s="1">
         <v>31445216</v>
@@ -9177,30 +9161,46 @@
         <v>382</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R66" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
@@ -9221,55 +9221,41 @@
         <v>391</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
         <v>392</v>
       </c>
       <c r="I67" s="1"/>
-      <c r="J67" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>395</v>
-      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q67" s="1"/>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B68" s="1">
         <v>31447154</v>
@@ -9281,32 +9267,46 @@
         <v>391</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
         <v>392</v>
       </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>397</v>
+      </c>
       <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+      <c r="Q68" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U68" s="1"/>
       <c r="V68" s="1" t="s">
@@ -9335,31 +9335,43 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
+      <c r="M69" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
+      <c r="Q69" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R69" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" s="1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B70" s="1">
         <v>31455868</v>
@@ -9379,34 +9391,22 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>362</v>
-      </c>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>406</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
@@ -9522,34 +9522,46 @@
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>419</v>
+      </c>
       <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
+      <c r="Q73" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R73" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U73" s="1"/>
       <c r="V73" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B74" s="1">
         <v>31475270</v>
@@ -9564,11 +9576,13 @@
         <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="I74" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -9588,12 +9602,12 @@
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B75" s="1">
         <v>31475270</v>
@@ -9608,41 +9622,27 @@
         <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>425</v>
-      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
       <c r="P75" s="1"/>
-      <c r="Q75" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U75" s="1"/>
       <c r="V75" s="1" t="s">
@@ -9661,39 +9661,53 @@
         <v>428</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>362</v>
+      </c>
       <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
+      <c r="M76" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R76" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U76" s="1"/>
       <c r="V76" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" s="1" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B77" s="1">
         <v>31485048</v>
@@ -9703,44 +9717,30 @@
         <v>428</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>362</v>
-      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="P77" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U77" s="1"/>
       <c r="V77" s="1" t="s">
@@ -9942,10 +9942,10 @@
         <v>454</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>26</v>
@@ -9957,7 +9957,7 @@
         <v>29</v>
       </c>
       <c r="U81" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V81" s="1" t="s">
         <v>455</v>
@@ -9977,39 +9977,49 @@
         <v>458</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="J82" s="1" t="s">
+        <v>457</v>
+      </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>459</v>
+      </c>
       <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
+      <c r="Q82" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R82" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U82" s="1"/>
       <c r="V82" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B83" s="1">
         <v>31544182</v>
@@ -10021,40 +10031,30 @@
         <v>458</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
-        <v>457</v>
-      </c>
+      <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
-      <c r="M83" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>461</v>
-      </c>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
       <c r="P83" s="1"/>
-      <c r="Q83" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q83" s="1"/>
       <c r="R83" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1" t="s">
@@ -10177,39 +10177,53 @@
         <v>475</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1"/>
+      <c r="J86" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>478</v>
+      </c>
       <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
+      <c r="Q86" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R86" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U86" s="1"/>
       <c r="V86" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B87" s="1">
         <v>31758865</v>
@@ -10221,44 +10235,30 @@
         <v>475</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>480</v>
-      </c>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
-      <c r="Q87" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q87" s="1"/>
       <c r="R87" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U87" s="1"/>
       <c r="V87" s="1" t="s">
@@ -10278,7 +10278,7 @@
         <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>43</v>
@@ -10302,7 +10302,7 @@
         <v>486</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>487</v>
@@ -10387,13 +10387,13 @@
         <v>33</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H90" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>495</v>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>26</v>
@@ -10513,7 +10513,7 @@
       </c>
       <c r="P92" s="1"/>
       <c r="Q92" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>29</v>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>26</v>
@@ -10675,7 +10675,7 @@
         <v>530</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="L95" s="1" t="s">
         <v>111</v>
@@ -10691,7 +10691,7 @@
       </c>
       <c r="P95" s="1"/>
       <c r="Q95" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R95" s="1" t="s">
         <v>26</v>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>26</v>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>26</v>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>26</v>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>26</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>29</v>
@@ -11085,7 +11085,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>26</v>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>26</v>
@@ -11242,7 +11242,7 @@
         <v>322</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>590</v>
@@ -11294,10 +11294,10 @@
       </c>
       <c r="I106" s="1"/>
       <c r="J106" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>597</v>
@@ -11313,7 +11313,7 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R106" s="1" t="s">
         <v>26</v>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>26</v>
@@ -11433,7 +11433,7 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>26</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>26</v>
@@ -11763,7 +11763,7 @@
         <v>29</v>
       </c>
       <c r="U114" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V114" s="1" t="s">
         <v>645</v>
@@ -11852,7 +11852,7 @@
         <v>442</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>656</v>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R116" s="1" t="s">
         <v>26</v>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R118" s="1" t="s">
         <v>26</v>
@@ -12058,7 +12058,7 @@
         <v>88</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>673</v>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>26</v>
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>29</v>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R122" s="1" t="s">
         <v>26</v>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>26</v>
@@ -12348,7 +12348,7 @@
         <v>88</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M125" s="1"/>
       <c r="N125" s="1" t="s">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R125" s="1" t="s">
         <v>26</v>
@@ -12403,10 +12403,10 @@
         <v>713</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M126" s="1"/>
       <c r="N126" s="1" t="s">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R129" s="1" t="s">
         <v>26</v>
@@ -12631,7 +12631,7 @@
         <v>33</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H130" s="1"/>
       <c r="I130" s="1"/>
@@ -12683,7 +12683,7 @@
         <v>744</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L131" s="1" t="s">
         <v>745</v>
@@ -12739,7 +12739,7 @@
         <v>751</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L132" s="1" t="s">
         <v>111</v>
@@ -12813,7 +12813,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>26</v>
@@ -12869,7 +12869,7 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R134" s="1" t="s">
         <v>26</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>26</v>
@@ -13040,7 +13040,7 @@
         <v>26</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G138" s="1"/>
       <c r="H138" s="1"/>
@@ -13058,7 +13058,7 @@
         <v>782</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O138" s="1" t="s">
         <v>783</v>
@@ -13097,13 +13097,13 @@
         <v>33</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H139" s="1" t="s">
         <v>786</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
@@ -13156,7 +13156,7 @@
         <v>322</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M140" s="1"/>
       <c r="N140" s="1" t="s">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>26</v>
@@ -13212,7 +13212,7 @@
         <v>322</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>797</v>
@@ -13225,7 +13225,7 @@
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R141" s="1" t="s">
         <v>26</v>
@@ -13283,7 +13283,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>26</v>
@@ -13542,7 +13542,7 @@
         <v>322</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>832</v>
@@ -13611,7 +13611,7 @@
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>26</v>
@@ -13660,7 +13660,7 @@
         <v>88</v>
       </c>
       <c r="L149" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M149" s="1" t="s">
         <v>845</v>
@@ -13731,7 +13731,7 @@
         <v>854</v>
       </c>
       <c r="Q150" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>26</v>
@@ -13789,7 +13789,7 @@
         <v>861</v>
       </c>
       <c r="Q151" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>26</v>
@@ -13851,7 +13851,7 @@
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R152" s="1" t="s">
         <v>26</v>
@@ -14067,7 +14067,7 @@
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>26</v>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="P158" s="1"/>
       <c r="Q158" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R158" s="1" t="s">
         <v>26</v>
@@ -14237,7 +14237,7 @@
       </c>
       <c r="P159" s="1"/>
       <c r="Q159" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R159" s="1" t="s">
         <v>26</v>
@@ -14282,7 +14282,7 @@
         <v>110</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M160" s="1" t="s">
         <v>916</v>
@@ -14326,7 +14326,7 @@
         <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G161" s="1" t="s">
         <v>43</v>
@@ -14350,14 +14350,14 @@
         <v>922</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O161" s="1" t="s">
         <v>926</v>
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R161" s="1" t="s">
         <v>26</v>
@@ -14462,7 +14462,7 @@
         <v>322</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>937</v>
@@ -14577,7 +14577,7 @@
       </c>
       <c r="P165" s="1"/>
       <c r="Q165" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R165" s="1" t="s">
         <v>26</v>
@@ -14606,7 +14606,7 @@
         <v>26</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -14715,7 +14715,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>26</v>
@@ -14756,7 +14756,7 @@
         <v>88</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M169" s="1" t="s">
         <v>963</v>
@@ -14869,7 +14869,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>26</v>
@@ -14898,7 +14898,7 @@
         <v>26</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G172" s="1"/>
       <c r="H172" s="1"/>
@@ -14938,7 +14938,7 @@
         <v>26</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>43</v>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>26</v>
@@ -15096,7 +15096,7 @@
         <v>322</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>990</v>
@@ -15109,7 +15109,7 @@
       </c>
       <c r="P176" s="1"/>
       <c r="Q176" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>26</v>
@@ -15278,7 +15278,7 @@
         <v>26</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -15296,7 +15296,7 @@
         <v>1008</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>1009</v>
@@ -15393,7 +15393,7 @@
         <v>1018</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J182" s="1" t="s">
         <v>1019</v>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>26</v>
@@ -15695,7 +15695,7 @@
         <v>1053</v>
       </c>
       <c r="Q187" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R187" s="1" t="s">
         <v>26</v>
@@ -15751,7 +15751,7 @@
       </c>
       <c r="P188" s="1"/>
       <c r="Q188" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R188" s="1" t="s">
         <v>26</v>
@@ -15785,13 +15785,13 @@
         <v>33</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H189" s="1" t="s">
         <v>1062</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J189" s="1"/>
       <c r="K189" s="1"/>
@@ -15859,7 +15859,7 @@
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>26</v>
@@ -15973,7 +15973,7 @@
       </c>
       <c r="P192" s="1"/>
       <c r="Q192" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R192" s="1" t="s">
         <v>26</v>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R194" s="1" t="s">
         <v>26</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R196" s="1" t="s">
         <v>26</v>
@@ -16298,7 +16298,7 @@
         <v>88</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>313</v>
@@ -16311,7 +16311,7 @@
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>26</v>
@@ -16634,7 +16634,7 @@
         <v>1152</v>
       </c>
       <c r="L204" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M204" s="1"/>
       <c r="N204" s="1" t="s">
@@ -16676,7 +16676,7 @@
         <v>26</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G205" s="1"/>
       <c r="H205" s="1"/>
@@ -16848,7 +16848,7 @@
         <v>521</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M208" s="1" t="s">
         <v>1173</v>
@@ -17009,7 +17009,7 @@
         <v>1192</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>26</v>
@@ -17053,7 +17053,7 @@
         <v>1198</v>
       </c>
       <c r="K212" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="L212" s="1" t="s">
         <v>217</v>
@@ -17098,7 +17098,7 @@
         <v>26</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="G213" s="1"/>
       <c r="H213" s="1"/>
@@ -17110,11 +17110,11 @@
         <v>257</v>
       </c>
       <c r="L213" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M213" s="1"/>
       <c r="N213" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1204</v>
@@ -17218,7 +17218,7 @@
         <v>322</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1210</v>
@@ -17231,7 +17231,7 @@
       </c>
       <c r="P215" s="1"/>
       <c r="Q215" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R215" s="1" t="s">
         <v>26</v>
@@ -17401,7 +17401,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>26</v>
@@ -17481,7 +17481,7 @@
         <v>33</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>1240</v>
@@ -17635,7 +17635,7 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R222" s="1" t="s">
         <v>26</v>
@@ -17669,13 +17669,13 @@
         <v>33</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J223" s="1" t="s">
         <v>1262</v>
@@ -17753,7 +17753,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -17787,13 +17787,13 @@
         <v>33</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H225" s="1" t="s">
         <v>1273</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J225" s="1" t="s">
         <v>1274</v>
@@ -17817,7 +17817,7 @@
         <v>1277</v>
       </c>
       <c r="Q225" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>26</v>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>26</v>
@@ -18083,7 +18083,7 @@
         <v>1228</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H230" s="1"/>
       <c r="I230" s="1"/>
@@ -18152,7 +18152,7 @@
         <v>1152</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>1314</v>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>26</v>
@@ -18212,7 +18212,7 @@
         <v>1152</v>
       </c>
       <c r="L232" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M232" s="1" t="s">
         <v>1319</v>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>26</v>
@@ -18297,7 +18297,7 @@
         <v>29</v>
       </c>
       <c r="U233" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V233" s="1" t="s">
         <v>1331</v>
@@ -18531,7 +18531,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>26</v>
@@ -18603,7 +18603,7 @@
         <v>29</v>
       </c>
       <c r="U238" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V238" s="1" t="s">
         <v>1362</v>
@@ -18639,7 +18639,7 @@
         <v>1367</v>
       </c>
       <c r="K239" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="L239" s="1" t="s">
         <v>217</v>
@@ -18693,13 +18693,13 @@
         <v>33</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>1374</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>1375</v>
@@ -18774,7 +18774,7 @@
         <v>1384</v>
       </c>
       <c r="L241" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M241" s="1" t="s">
         <v>1385</v>
@@ -19095,7 +19095,7 @@
       </c>
       <c r="P246" s="1"/>
       <c r="Q246" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R246" s="1" t="s">
         <v>26</v>
@@ -19159,7 +19159,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>26</v>
@@ -19223,7 +19223,7 @@
       </c>
       <c r="P248" s="1"/>
       <c r="Q248" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>26</v>
@@ -19267,7 +19267,7 @@
         <v>1440</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L249" s="1" t="s">
         <v>781</v>
@@ -19381,13 +19381,13 @@
         <v>33</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H251" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J251" s="1" t="s">
         <v>1452</v>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>26</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>26</v>
@@ -19580,7 +19580,7 @@
         <v>1473</v>
       </c>
       <c r="L254" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="M254" s="1" t="s">
         <v>1469</v>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>26</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R255" s="1" t="s">
         <v>29</v>
@@ -19727,7 +19727,7 @@
         <v>29</v>
       </c>
       <c r="U256" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V256" s="1" t="s">
         <v>1493</v>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R257" s="1" t="s">
         <v>26</v>
@@ -19833,7 +19833,7 @@
       </c>
       <c r="P258" s="1"/>
       <c r="Q258" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R258" s="1" t="s">
         <v>26</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>26</v>
@@ -19951,7 +19951,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>26</v>
@@ -20017,7 +20017,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>26</v>
@@ -20171,13 +20171,13 @@
         <v>33</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>1543</v>
@@ -20310,7 +20310,7 @@
         <v>1561</v>
       </c>
       <c r="L266" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="M266" s="1" t="s">
         <v>1562</v>
@@ -20335,7 +20335,7 @@
         <v>29</v>
       </c>
       <c r="U266" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V266" s="1" t="s">
         <v>1564</v>
@@ -20385,7 +20385,7 @@
       </c>
       <c r="P267" s="1"/>
       <c r="Q267" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R267" s="1" t="s">
         <v>26</v>
@@ -20429,10 +20429,10 @@
         <v>1569</v>
       </c>
       <c r="K268" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1567</v>
@@ -20517,7 +20517,7 @@
         <v>29</v>
       </c>
       <c r="U269" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V269" s="1" t="s">
         <v>1582</v>
@@ -20556,7 +20556,7 @@
         <v>1359</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1587</v>
@@ -20581,7 +20581,7 @@
         <v>29</v>
       </c>
       <c r="U270" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V270" s="1" t="s">
         <v>1589</v>
@@ -20615,10 +20615,10 @@
         <v>1594</v>
       </c>
       <c r="K271" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1592</v>
@@ -20675,10 +20675,10 @@
         <v>1594</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1599</v>
@@ -20765,7 +20765,7 @@
         <v>29</v>
       </c>
       <c r="U273" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V273" s="1" t="s">
         <v>1610</v>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>26</v>
@@ -20879,7 +20879,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>26</v>
@@ -20891,7 +20891,7 @@
         <v>29</v>
       </c>
       <c r="U275" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="V275" s="1" t="s">
         <v>1629</v>
@@ -21065,7 +21065,7 @@
         <v>29</v>
       </c>
       <c r="U278" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V278" s="1" t="s">
         <v>1652</v>
@@ -21113,7 +21113,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>26</v>
@@ -21162,7 +21162,7 @@
         <v>1664</v>
       </c>
       <c r="L280" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M280" s="1" t="s">
         <v>1661</v>
